--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5257,6 +5257,11 @@
           <t>฿65.00</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>done 2026-09-13 21:51</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -6233,7 +6238,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["D", "A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ"], "last_roles": ["R2", "R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มู่ลี่ไม้ โซ่วน ใบ50mm สั่งผลิตตามขนาด ราคาแค่ 1199 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง"], "last_styles": ["การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล"], "last_roles": ["R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5312,6 +5312,11 @@
           <t>฿17.00</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>done 2026-09-14 23:51</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -6238,7 +6243,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง"], "last_styles": ["การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล"], "last_roles": ["R5", "R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แก้วน้ำเก็บอุณหภูมิ Sanrio น่ารัก ขนาดใหญ่ ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ"], "last_roles": ["R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5342,6 +5342,11 @@
           <t>฿21.00</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>done 2026-09-15 22:29</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -6243,7 +6248,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ"], "last_roles": ["R6", "R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง REAIM เครื่องฉีดน้ำแรงดันสูง อัดฉีด ฉีดล้าง ราคาแค่ 1149 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก"], "last_roles": ["R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5372,6 +5372,11 @@
           <t>฿11.00</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>done 2026-09-16 22:22</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -6248,7 +6253,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก"], "last_roles": ["R8", "R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ เครื่องนอน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 1039 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้"], "last_styles": ["การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ"], "last_roles": ["R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7"], "recent_captions": ["มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5427,6 +5427,11 @@
           <t>฿11.00</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>done 2026-09-17 22:28</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -6253,7 +6258,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้"], "last_styles": ["การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ"], "last_roles": ["R5", "R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7"], "recent_captions": ["มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ เก้าอี้สุขภาพ แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TENGU เก้าอี้Sanrio ลิขสิทธิ์แท้ซานริโอ้มีเจ้ ราคาแค่ 3890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้"], "last_styles": ["การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ"], "last_roles": ["R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5"], "recent_captions": ["อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5457,6 +5457,11 @@
           <t>฿9.00</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>done 2026-09-18 21:50</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -6258,7 +6263,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้"], "last_styles": ["การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ"], "last_roles": ["R5", "R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5"], "recent_captions": ["อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ แถมพลั่ว กระทะ กระทะเคลือบหินอ่อน กระทะหินอ่อ ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E"], "last_hooks": ["ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ"], "last_roles": ["R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7"], "recent_captions": ["ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G217"/>
+  <dimension ref="A1:G221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6235,6 +6235,106 @@
       <c r="F217" t="inlineStr">
         <is>
           <t>฿4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>131</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ประสิทธิภาพระดับท็อป กล้องซูมคมชัด ดีไซน์พรีเมียม สั่งซื้อผ่าน Apple Flagship Store พร้อมรับโค้ดส่วนลดและผ่อน 0% SpayLater</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8AWCoHKL6C</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztn-msxxsasoiscl48</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>฿48,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>132</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Apple iPhone 17 Pro (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A19 Pro หน้าจอ ProMotion 120Hz แบตเตอรี่อึดยิ่งขึ้น ระบบกล้องโปร เครื่องศูนย์แท้พร้อมประกันศูนย์ไทย</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5AsbEphgh5</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztf-msuyb0tv79qff4</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>฿39,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>133</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Apple iPhone 16 Plus (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) จอใหญ่เต็มตา แบตเตอรี่อึดทนทาน รองรับ Apple Intelligence เต็มรูปแบบ ชิป A18 เครื่องศูนย์ไทยแท้</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LnLTzHQeV</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-81ztg-msuy0uk4gkjo7b</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>฿34,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>134</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15 (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) พอร์ต USB-C กล้องหลัก 48MP หน้าจอ Dynamic Island คุ้มค่าที่สุดสำหรับรุ่นมาตรฐาน ใช้งานได้ยาวนาน</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fSTPKxXrZ</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://store.storeimages.cdn-apple.com/8756/as-images.apple.com/is/iphone-15-finish-select-202309-6-1inch-black?wid=5120&amp;hei=2880&amp;fmt=p-jpg&amp;qlt=80&amp;.v=1692923777972</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>฿26,900.00</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ประสิทธิภาพระดับท็อป กล้องซูมคมชัด ดีไซน์พรีเมียม สั่งซื้อผ่าน Apple Flagship Store พร้อมรับโค้ดส่วนลดและผ่อน 0% SpayLater</t>
+          <t>Apple iPhone 18 Pro Max (เครื่องศูนย์ไทย ประกันศูนย์ 1 ปี) ชิป A20 Pro ร้านค้าทางการ Shopee Mall มั่นใจได้ของแท้ 100% ประกันศูนย์ไทยเต็มปี ไม่เสี่ยงเครื่องย้อมแมว ซื้อของราคาสูงเลือกร้าน Mall อุ่นใจ ปลอดภัยที่สุด</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G221"/>
+  <dimension ref="A1:G239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6335,6 +6335,466 @@
       <c r="F221" t="inlineStr">
         <is>
           <t>฿26,900.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>135</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>ทีวี 32 นิ้ว ทีวี 43 นิ้ว Smart TV 4K LED โทรทัศน์ ทีวีจอแบน สมาร์ททีวี ระบบ Android ทีวีดิจิตอล รับประกัน 1ปี ราคา 3689.00 บาท</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VrqMwDZNm</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mp3uikhs59n0d1.webp</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>ลด 73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>136</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>New เสื้อฮู้ด Stussy Hoodie แท้100% สําหรับผู้ชาย และผู้หญิง หลวมเสื้อฮู้ด ราคา 1680.00 บาท</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B7XABAYi0</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mln7lyct3shvb7.webp</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>ลด 42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>137</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Lifinity ชั้นวางจาน ที่คว่ำจาน 120/105ซม ชั้นวางของในครัว ราคา 678.00 บาท</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qc9ZkOEib</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m6m8v000vb5b5e.webp</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>ลด 55%</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>138</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>XTREM เคส iPhone 18/17/16/15/14 เปลี่ยนรูปได้ เคสเปลี่ยนรูป เคสไอโฟน เคสมือถือ Magnetic Screen Case NFC จอ E-Ink ราคา 2250.00 บาท</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6q0pWwhhQ9</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8259f-mt18gjog1xj6a4.webp</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>ลด 35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>139</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Pacsafe CX Anti-Theft Square Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน | Fits 8" Tablet ราคา 4100.00 บาท</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VzJBAKIWf</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-msmmfx079j4163.webp</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>ลด 45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>140</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>BOYA mini 2 ไมค์ไร้สาย ตัดเสียงรบกวน AI ไมค์อัดเสียง สําหรับ Type-C iPhone/Android ไมค์ไลฟ์สด ราคา 1319.00 บาท</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AOkJG7XeU</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-miwe8y7c5edg26.webp</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>ลด 39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>141</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>[HOT]AXON Mega Smart Watch จอใหญ่AMOLED 1.85",แบตอึด,โทรได้,วัดชีพจร SpO2 ,วัดการนอน,โหมดออกกำลังกาย100+, IP68 ประกัน2ปี ราคา 1798.00 บาท</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1AVOUsEit</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mpj9ta3nkqvj7a.webp</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>ลด 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>142</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Pacsafe GO Anti-Theft Saddle Crossbody กระเป๋ากันขโมย กระเป๋าสะพายข้าง สำหรับเดินทางและใช้งานทุกวัน ราคา 4730.00 บาท</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Vcukm6B7Q</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-msmlbhosfs3o57.webp</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>143</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>[ซื้อ 1 แถม 6] 2026 แท็บเล็ตพีซี 12.0 นิ้ว 12000mAh แบตเตอรี่ 4G / 5G แท็บเล็ต Dual SIM Android 12.0 แท็บเล็ต COD ราคา 1799.00 บาท</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60RiXXMOj0</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mhlffavqeo7c65.webp</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>144</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ANCHI จักรยานพับได้ จักรยานแม่บ้าน จักรยาน แม่บ้าน ญี่ปุ่น เกียร์ 7 ระดับ ตะกร้าเหล็ก จักรยานผู้ใหญ ราคา 1955.00 บาท</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4B04MAcB1P</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mlw25x1168zm9d.webp</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>ลด 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>145</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Hisense TV 55 นิ้ว รุ่น 55E6Q 4K Ultra HD Smart TV Voice Control WIFI Build in Netflix ราคา 9490.00 บาท</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50ZBLhh7GG</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mt5hov1ntfr612.webp</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>ลด 41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>146</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>เครื่องตัดกิ่งไม้ไร้สาย ตัดแต่งพุ่มไม้ แต่งกิ่งไม้ เครื่องตัดหญ้าไฟฟ้า เลื่อยตัดแต่งสวน ตัดแต่งพุ่มหญ้า ราคา 875.00 บาท</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KiAVfeVSA</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul9-ljuyqy4onhnq0b.webp</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>ลด 45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>147</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>【รับประกัน 5ปี】elago เครื่องตัดหญ้าไฟฟ้าไร้สาย แบบพกพา ปรับได้ ยืดหด 5000mAh*2 อุปกรณ์ครบชุด พร้อมแบตเตอรีลิเธียมแท้ ราคา 634.00 บาท</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VVRwdnTF3</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mq1py5gj48ox05.webp</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>ลด 15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>148</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>XTREM เคส iPhone 17 เปลี่ยนรูปได้ เคสเปลี่ยนรูป เคสมือถือ เคสไอโฟน Magnetic Screen Case NFC หน้าจอ E-Ink ราคา 2750.00 บาท</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fZwWdSAZ8</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-msy2myjf83rbdd.webp</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>ลด 37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>149</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>[Best Seller] TCL แอร์ Full DC SaveIn AI Inverter ประหยัดไฟ ขนาด 9,200- 24,200 BTU รุ่น TAC-XALCH2 ราคา 14290.00 บาท</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zxrIvShk4</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-msjawf9q8e808c.webp</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>ลด 19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>150</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>เคส iPhone 18 Pro Max 18 Pro 17 Air 16 Series Ultra Hybrid T MagFit Spigen - รองรับ Camera Control ราคา 1287.00 บาท</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4VcukpE2bD</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134207-825am-msxh4293k0sp86.webp</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>ลด 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>151</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>KEEN รองเท้าแตะรัดส้น ชายหญิง กันกระแทกส้นและนิ้วเท้า กันลื่นยางแท้ทุกพื้น เป่าไว ซับนิ่ม เดินป่าทางชัน ราคา 2429.00 บาท</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LYQAr4Hov</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-moggu9b4ekn405.webp</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>ลด 53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>152</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2024 สไตล ์ ใหม ่ Star alpinestars a รถจักรยานยนต ์ Warm Shock-resistant Cycling Jersey Casual แจ ็ คเก ็ ตผู ้ ชายผู ้ หญิงฤดูใบไม ้ ผลิฤดูใบไม ้ ร ่ วงฤดูหนาว Soft Shell แจ ็ คเก ็ ตกันน ้ ํา Star แจ ็ คเก ็ ตสองสี ราคา 2107.00 บาท</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VkNZ0QFA2</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-luf6vg0dv0xw51.webp</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>ลด 38%</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -6262,6 +6262,11 @@
           <t>฿48,900.00</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>done 2026-09-19 21:14</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -6352,7 +6357,6 @@
           <t>https://s.shopee.co.th/2VrqMwDZNm</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mp3uikhs59n0d1.webp</t>
@@ -6378,7 +6382,6 @@
           <t>https://s.shopee.co.th/3B7XABAYi0</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mln7lyct3shvb7.webp</t>
@@ -6404,7 +6407,6 @@
           <t>https://s.shopee.co.th/1qc9ZkOEib</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m6m8v000vb5b5e.webp</t>
@@ -6430,7 +6432,6 @@
           <t>https://s.shopee.co.th/6q0pWwhhQ9</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-8259f-mt18gjog1xj6a4.webp</t>
@@ -6456,7 +6457,6 @@
           <t>https://s.shopee.co.th/1VzJBAKIWf</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-msmmfx079j4163.webp</t>
@@ -6482,7 +6482,6 @@
           <t>https://s.shopee.co.th/9AOkJG7XeU</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-miwe8y7c5edg26.webp</t>
@@ -6508,7 +6507,6 @@
           <t>https://s.shopee.co.th/1AVOUsEit</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mpj9ta3nkqvj7a.webp</t>
@@ -6534,13 +6532,11 @@
           <t>https://s.shopee.co.th/4Vcukm6B7Q</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-msmlbhosfs3o57.webp</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -6556,13 +6552,11 @@
           <t>https://s.shopee.co.th/60RiXXMOj0</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mhlffavqeo7c65.webp</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -6578,7 +6572,6 @@
           <t>https://s.shopee.co.th/4B04MAcB1P</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mlw25x1168zm9d.webp</t>
@@ -6604,7 +6597,6 @@
           <t>https://s.shopee.co.th/50ZBLhh7GG</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mt5hov1ntfr612.webp</t>
@@ -6630,7 +6622,6 @@
           <t>https://s.shopee.co.th/9KiAVfeVSA</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul9-ljuyqy4onhnq0b.webp</t>
@@ -6656,7 +6647,6 @@
           <t>https://s.shopee.co.th/5VVRwdnTF3</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mq1py5gj48ox05.webp</t>
@@ -6682,7 +6672,6 @@
           <t>https://s.shopee.co.th/7fZwWdSAZ8</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-msy2myjf83rbdd.webp</t>
@@ -6708,7 +6697,6 @@
           <t>https://s.shopee.co.th/9zxrIvShk4</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-msjawf9q8e808c.webp</t>
@@ -6734,7 +6722,6 @@
           <t>https://s.shopee.co.th/4VcukpE2bD</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134207-825am-msxh4293k0sp86.webp</t>
@@ -6760,7 +6747,6 @@
           <t>https://s.shopee.co.th/2LYQAr4Hov</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-moggu9b4ekn405.webp</t>
@@ -6786,7 +6772,6 @@
           <t>https://s.shopee.co.th/3VkNZ0QFA2</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-luf6vg0dv0xw51.webp</t>
@@ -6823,7 +6808,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E"], "last_hooks": ["ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ"], "last_roles": ["R4", "R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7"], "recent_captions": ["ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ZINSANO เครื่องฉีดน้ำแรงดันสูง - บาร์ ราคาแค่ 4290 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง"], "last_styles": ["มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ"], "last_roles": ["R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8"], "recent_captions": ["โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5487,6 +5487,11 @@
           <t>฿97.00</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>done 2026-09-20 21:37</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -6808,7 +6813,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D"], "last_hooks": ["โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง"], "last_styles": ["มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ"], "last_roles": ["R4", "R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8"], "recent_captions": ["โดนป้ายยามาอีกที สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ห่อ Botare GB/T Air ราคาแค่ 174 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ"], "last_styles": ["การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ"], "last_roles": ["R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -6297,6 +6297,11 @@
           <t>฿39,900.00</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>done 2026-09-21 23:52</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -6813,7 +6818,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["D", "D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ"], "last_styles": ["การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ"], "last_roles": ["R1", "R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ SOLOMON ที่นอนยางพารา รุ่น Sunshine ราคาแค่ 4083 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": false}</t>
+          <t>{"last_personas": ["D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G", "A"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ", "เทียบข้อมูล"], "last_roles": ["R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7", "R6"], "recent_captions": ["เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่กำลังมองหาสมาร์ตโฟนสเปกแรง การเลือกรุ่นราคาสูงอย่าง iPhone 17 Pro ราคา 39,900 บาท ผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องหิ้วหรือโดนโกงเรื่องบริการหลังการขายครับ ผมอยากถามคนที่เคยใช้งานจริงว่าชิป A19 Pro ควบคู่กับจอ ProMotion 120Hz เวลาเปิดกราฟิกสูงต่อเนื่อง มีอาการหน่วงหรือแบตเตอรี่ลดไวกว่าปกติไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5517,6 +5517,11 @@
           <t>฿14.00</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>done 2026-09-22 22:28</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -6818,7 +6823,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["D", "B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G", "A"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ", "เทียบข้อมูล"], "last_roles": ["R5", "R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7", "R6"], "recent_captions": ["เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ DreaME in โซฟาเบดแบบพับได้ ฟองน้ำความหนาแน่นส ราคาแค่ 5099 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่กำลังมองหาสมาร์ตโฟนสเปกแรง การเลือกรุ่นราคาสูงอย่าง iPhone 17 Pro ราคา 39,900 บาท ผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องหิ้วหรือโดนโกงเรื่องบริการหลังการขายครับ ผมอยากถามคนที่เคยใช้งานจริงว่าชิป A19 Pro ควบคู่กับจอ ProMotion 120Hz เวลาเปิดกราฟิกสูงต่อเนื่อง มีอาการหน่วงหรือแบตเตอรี่ลดไวกว่าปกติไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G", "A", "E"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้"], "last_styles": ["มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ", "เทียบข้อมูล", "ปัญหาและทางเลือก"], "last_roles": ["R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7", "R6", "R3"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่กำลังมองหาสมาร์ตโฟนสเปกแรง การเลือกรุ่นราคาสูงอย่าง iPhone 17 Pro ราคา 39,900 บาท ผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องหิ้วหรือโดนโกงเรื่องบริการหลังการขายครับ ผมอยากถามคนที่เคยใช้งานจริงว่าชิป A19 Pro ควบคู่กับจอ ProMotion 120Hz เวลาเปิดกราฟิกสูงต่อเนื่อง มีอาการหน่วงหรือแบตเตอรี่ลดไวกว่าปกติไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่าย 14 บาทแล้วได้ขวดเครื่องปรุงที่มีช้อนตักในตัว ผมว่าก็น่าสนใจสำหรับคนที่เจอปัญหาช้อนจมหายหรือเลอะเทอะเวลาหยิบใช้ครับ คิดว่าขวดเครื่องปรุงราคา 14 บาทที่มีฟังก์ชันช้อนในตัวแบบนี้จะตักใช้งานได้สะดวกจริงไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -6332,6 +6332,11 @@
           <t>฿34,900.00</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>done 2026-09-23 22:22</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -6823,7 +6828,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G", "A", "E"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้"], "last_styles": ["มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ", "เทียบข้อมูล", "ปัญหาและทางเลือก"], "last_roles": ["R3", "R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7", "R6", "R3"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ โซฟาขี้เกียจ Bean Bag บีนแบ็ก ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่กำลังมองหาสมาร์ตโฟนสเปกแรง การเลือกรุ่นราคาสูงอย่าง iPhone 17 Pro ราคา 39,900 บาท ผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องหิ้วหรือโดนโกงเรื่องบริการหลังการขายครับ ผมอยากถามคนที่เคยใช้งานจริงว่าชิป A19 Pro ควบคู่กับจอ ProMotion 120Hz เวลาเปิดกราฟิกสูงต่อเนื่อง มีอาการหน่วงหรือแบตเตอรี่ลดไวกว่าปกติไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่าย 14 บาทแล้วได้ขวดเครื่องปรุงที่มีช้อนตักในตัว ผมว่าก็น่าสนใจสำหรับคนที่เจอปัญหาช้อนจมหายหรือเลอะเทอะเวลาหยิบใช้ครับ คิดว่าขวดเครื่องปรุงราคา 14 บาทที่มีฟังก์ชันช้อนในตัวแบบนี้จะตักใช้งานได้สะดวกจริงไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": false}</t>
+          <t>{"last_personas": ["G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G", "A", "E", "B"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ", "เทียบข้อมูล", "ปัญหาและทางเลือก", "บอกต่อแบบกลางๆ"], "last_roles": ["R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7", "R6", "R3", "R6"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่กำลังมองหาสมาร์ตโฟนสเปกแรง การเลือกรุ่นราคาสูงอย่าง iPhone 17 Pro ราคา 39,900 บาท ผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องหิ้วหรือโดนโกงเรื่องบริการหลังการขายครับ ผมอยากถามคนที่เคยใช้งานจริงว่าชิป A19 Pro ควบคู่กับจอ ProMotion 120Hz เวลาเปิดกราฟิกสูงต่อเนื่อง มีอาการหน่วงหรือแบตเตอรี่ลดไวกว่าปกติไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่าย 14 บาทแล้วได้ขวดเครื่องปรุงที่มีช้อนตักในตัว ผมว่าก็น่าสนใจสำหรับคนที่เจอปัญหาช้อนจมหายหรือเลอะเทอะเวลาหยิบใช้ครับ คิดว่าขวดเครื่องปรุงราคา 14 บาทที่มีฟังก์ชันช้อนในตัวแบบนี้จะตักใช้งานได้สะดวกจริงไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหาแบตมือถือหมดไวระหว่างวัน การเลือกซื้อสมาร์ตโฟนราคาสูงอย่าง iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ชิป A18 ในราคา 34,900 บาท ผ่านร้านค้าทางการ Apple Flagship Store บน Shopee Mall ทำให้ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวและอุ่นใจเรื่องบริการหลังการขายครับ \n\nคนที่ใช้งานจริงอยู่ อยากทราบว่าชิป A18 ตัวนี้ช่วยจัดการพลังงานให้แบตเตอรี่ใช้งานทั่วไปพ้นวันโดยไม่ต้องพกที่ชาร์จสำรองได้จริงไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5547,6 +5547,11 @@
           <t>฿69.00</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>done 2026-09-24 22:45</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -6828,7 +6833,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G", "A", "E", "B"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ", "เทียบข้อมูล", "ปัญหาและทางเลือก", "บอกต่อแบบกลางๆ"], "last_roles": ["R2", "R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7", "R6", "R3", "R6"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ เครื่องมือช่าง/ทำสวน ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Maybuck เครื่องตัดหญ้าเบนซิน GX- จังหวะสำหรับ ราคาแค่ 2680 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่กำลังมองหาสมาร์ตโฟนสเปกแรง การเลือกรุ่นราคาสูงอย่าง iPhone 17 Pro ราคา 39,900 บาท ผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องหิ้วหรือโดนโกงเรื่องบริการหลังการขายครับ ผมอยากถามคนที่เคยใช้งานจริงว่าชิป A19 Pro ควบคู่กับจอ ProMotion 120Hz เวลาเปิดกราฟิกสูงต่อเนื่อง มีอาการหน่วงหรือแบตเตอรี่ลดไวกว่าปกติไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่าย 14 บาทแล้วได้ขวดเครื่องปรุงที่มีช้อนตักในตัว ผมว่าก็น่าสนใจสำหรับคนที่เจอปัญหาช้อนจมหายหรือเลอะเทอะเวลาหยิบใช้ครับ คิดว่าขวดเครื่องปรุงราคา 14 บาทที่มีฟังก์ชันช้อนในตัวแบบนี้จะตักใช้งานได้สะดวกจริงไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหาแบตมือถือหมดไวระหว่างวัน การเลือกซื้อสมาร์ตโฟนราคาสูงอย่าง iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ชิป A18 ในราคา 34,900 บาท ผ่านร้านค้าทางการ Apple Flagship Store บน Shopee Mall ทำให้ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวและอุ่นใจเรื่องบริการหลังการขายครับ \n\nคนที่ใช้งานจริงอยู่ อยากทราบว่าชิป A18 ตัวนี้ช่วยจัดการพลังงานให้แบตเตอรี่ใช้งานทั่วไปพ้นวันโดยไม่ต้องพกที่ชาร์จสำรองได้จริงไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G", "A", "E", "B", "F"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล"], "last_styles": ["การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ", "เทียบข้อมูล", "ปัญหาและทางเลือก", "บอกต่อแบบกลางๆ", "เทียบข้อมูล"], "last_roles": ["R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7", "R6", "R3", "R6", "R7"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่กำลังมองหาสมาร์ตโฟนสเปกแรง การเลือกรุ่นราคาสูงอย่าง iPhone 17 Pro ราคา 39,900 บาท ผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องหิ้วหรือโดนโกงเรื่องบริการหลังการขายครับ ผมอยากถามคนที่เคยใช้งานจริงว่าชิป A19 Pro ควบคู่กับจอ ProMotion 120Hz เวลาเปิดกราฟิกสูงต่อเนื่อง มีอาการหน่วงหรือแบตเตอรี่ลดไวกว่าปกติไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่าย 14 บาทแล้วได้ขวดเครื่องปรุงที่มีช้อนตักในตัว ผมว่าก็น่าสนใจสำหรับคนที่เจอปัญหาช้อนจมหายหรือเลอะเทอะเวลาหยิบใช้ครับ คิดว่าขวดเครื่องปรุงราคา 14 บาทที่มีฟังก์ชันช้อนในตัวแบบนี้จะตักใช้งานได้สะดวกจริงไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหาแบตมือถือหมดไวระหว่างวัน การเลือกซื้อสมาร์ตโฟนราคาสูงอย่าง iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ชิป A18 ในราคา 34,900 บาท ผ่านร้านค้าทางการ Apple Flagship Store บน Shopee Mall ทำให้ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวและอุ่นใจเรื่องบริการหลังการขายครับ \n\nคนที่ใช้งานจริงอยู่ อยากทราบว่าชิป A18 ตัวนี้ช่วยจัดการพลังงานให้แบตเตอรี่ใช้งานทั่วไปพ้นวันโดยไม่ต้องพกที่ชาร์จสำรองได้จริงไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สรุปข้อมูลของ แฟ้มเอกสาร ตัวนี้แบบสั้นๆ คือ 12 หน้า กันฝุ่นและความชื้น ราคา 69 บาทครับ ถ้าต้องเลือก แฟ้มเอกสาร สักตัว พี่ๆ ให้ความสำคัญกับจุดไหนที่สุดครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -6367,6 +6367,11 @@
           <t>฿26,900.00</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>done 2026-09-25 22:46</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -6833,7 +6838,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G", "A", "E", "B", "F"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล"], "last_styles": ["การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ", "เทียบข้อมูล", "ปัญหาและทางเลือก", "บอกต่อแบบกลางๆ", "เทียบข้อมูล"], "last_roles": ["R2", "R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7", "R6", "R3", "R6", "R7"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ เครื่องนอน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เตียงโซฟาพับ เตียงโซฟา เบดนอนด้วยการจัดเก็บปร ราคาแค่ 2541 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่กำลังมองหาสมาร์ตโฟนสเปกแรง การเลือกรุ่นราคาสูงอย่าง iPhone 17 Pro ราคา 39,900 บาท ผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องหิ้วหรือโดนโกงเรื่องบริการหลังการขายครับ ผมอยากถามคนที่เคยใช้งานจริงว่าชิป A19 Pro ควบคู่กับจอ ProMotion 120Hz เวลาเปิดกราฟิกสูงต่อเนื่อง มีอาการหน่วงหรือแบตเตอรี่ลดไวกว่าปกติไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่าย 14 บาทแล้วได้ขวดเครื่องปรุงที่มีช้อนตักในตัว ผมว่าก็น่าสนใจสำหรับคนที่เจอปัญหาช้อนจมหายหรือเลอะเทอะเวลาหยิบใช้ครับ คิดว่าขวดเครื่องปรุงราคา 14 บาทที่มีฟังก์ชันช้อนในตัวแบบนี้จะตักใช้งานได้สะดวกจริงไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหาแบตมือถือหมดไวระหว่างวัน การเลือกซื้อสมาร์ตโฟนราคาสูงอย่าง iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ชิป A18 ในราคา 34,900 บาท ผ่านร้านค้าทางการ Apple Flagship Store บน Shopee Mall ทำให้ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวและอุ่นใจเรื่องบริการหลังการขายครับ \n\nคนที่ใช้งานจริงอยู่ อยากทราบว่าชิป A18 ตัวนี้ช่วยจัดการพลังงานให้แบตเตอรี่ใช้งานทั่วไปพ้นวันโดยไม่ต้องพกที่ชาร์จสำรองได้จริงไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สรุปข้อมูลของ แฟ้มเอกสาร ตัวนี้แบบสั้นๆ คือ 12 หน้า กันฝุ่นและความชื้น ราคา 69 บาทครับ ถ้าต้องเลือก แฟ้มเอกสาร สักตัว พี่ๆ ให้ความสำคัญกับจุดไหนที่สุดครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": false}</t>
+          <t>{"last_personas": ["B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G", "A", "E", "B", "F", "G"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง"], "last_styles": ["การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ", "เทียบข้อมูล", "ปัญหาและทางเลือก", "บอกต่อแบบกลางๆ", "เทียบข้อมูล", "เทียบข้อมูล"], "last_roles": ["R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7", "R6", "R3", "R6", "R7", "R1"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่กำลังมองหาสมาร์ตโฟนสเปกแรง การเลือกรุ่นราคาสูงอย่าง iPhone 17 Pro ราคา 39,900 บาท ผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องหิ้วหรือโดนโกงเรื่องบริการหลังการขายครับ ผมอยากถามคนที่เคยใช้งานจริงว่าชิป A19 Pro ควบคู่กับจอ ProMotion 120Hz เวลาเปิดกราฟิกสูงต่อเนื่อง มีอาการหน่วงหรือแบตเตอรี่ลดไวกว่าปกติไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่าย 14 บาทแล้วได้ขวดเครื่องปรุงที่มีช้อนตักในตัว ผมว่าก็น่าสนใจสำหรับคนที่เจอปัญหาช้อนจมหายหรือเลอะเทอะเวลาหยิบใช้ครับ คิดว่าขวดเครื่องปรุงราคา 14 บาทที่มีฟังก์ชันช้อนในตัวแบบนี้จะตักใช้งานได้สะดวกจริงไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหาแบตมือถือหมดไวระหว่างวัน การเลือกซื้อสมาร์ตโฟนราคาสูงอย่าง iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ชิป A18 ในราคา 34,900 บาท ผ่านร้านค้าทางการ Apple Flagship Store บน Shopee Mall ทำให้ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวและอุ่นใจเรื่องบริการหลังการขายครับ \n\nคนที่ใช้งานจริงอยู่ อยากทราบว่าชิป A18 ตัวนี้ช่วยจัดการพลังงานให้แบตเตอรี่ใช้งานทั่วไปพ้นวันโดยไม่ต้องพกที่ชาร์จสำรองได้จริงไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สรุปข้อมูลของ แฟ้มเอกสาร ตัวนี้แบบสั้นๆ คือ 12 หน้า กันฝุ่นและความชื้น ราคา 69 บาทครับ ถ้าต้องเลือก แฟ้มเอกสาร สักตัว พี่ๆ ให้ความสำคัญกับจุดไหนที่สุดครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "คนที่ใช้งาน iPhone 15 ราคา 26,900 บาทอยู่ รู้สึกว่าพอร์ต USB-C กับกล้อง 48MP ช่วยให้ถ่ายโอนและจัดการไฟล์ภาพได้สะดวกกว่ารุ่นเดิมชัดเจนไหมครับ? สำหรับสมาร์ทโฟนราคาสูงแบบนี้ ผมมองว่าการเลือกซื้อเครื่องศูนย์ไทยแท้ที่มีประกันศูนย์ 1 ปีเต็มจากร้านค้าทางการ Shopee Mall มั่นใจได้ 100% เรื่องของแท้และบริการหลังการขาย ไม่ต้องเสี่ยงกับเครื่องย้อมแมวครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": true}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5577,6 +5577,11 @@
           <t>฿43.00</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>done 2026-09-26 21:56</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -6838,7 +6843,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G", "A", "E", "B", "F", "G"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง"], "last_styles": ["การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ", "เทียบข้อมูล", "ปัญหาและทางเลือก", "บอกต่อแบบกลางๆ", "เทียบข้อมูล", "เทียบข้อมูล"], "last_roles": ["R7", "R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7", "R6", "R3", "R6", "R7", "R1"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 675 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่กำลังมองหาสมาร์ตโฟนสเปกแรง การเลือกรุ่นราคาสูงอย่าง iPhone 17 Pro ราคา 39,900 บาท ผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องหิ้วหรือโดนโกงเรื่องบริการหลังการขายครับ ผมอยากถามคนที่เคยใช้งานจริงว่าชิป A19 Pro ควบคู่กับจอ ProMotion 120Hz เวลาเปิดกราฟิกสูงต่อเนื่อง มีอาการหน่วงหรือแบตเตอรี่ลดไวกว่าปกติไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่าย 14 บาทแล้วได้ขวดเครื่องปรุงที่มีช้อนตักในตัว ผมว่าก็น่าสนใจสำหรับคนที่เจอปัญหาช้อนจมหายหรือเลอะเทอะเวลาหยิบใช้ครับ คิดว่าขวดเครื่องปรุงราคา 14 บาทที่มีฟังก์ชันช้อนในตัวแบบนี้จะตักใช้งานได้สะดวกจริงไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหาแบตมือถือหมดไวระหว่างวัน การเลือกซื้อสมาร์ตโฟนราคาสูงอย่าง iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ชิป A18 ในราคา 34,900 บาท ผ่านร้านค้าทางการ Apple Flagship Store บน Shopee Mall ทำให้ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวและอุ่นใจเรื่องบริการหลังการขายครับ \n\nคนที่ใช้งานจริงอยู่ อยากทราบว่าชิป A18 ตัวนี้ช่วยจัดการพลังงานให้แบตเตอรี่ใช้งานทั่วไปพ้นวันโดยไม่ต้องพกที่ชาร์จสำรองได้จริงไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สรุปข้อมูลของ แฟ้มเอกสาร ตัวนี้แบบสั้นๆ คือ 12 หน้า กันฝุ่นและความชื้น ราคา 69 บาทครับ ถ้าต้องเลือก แฟ้มเอกสาร สักตัว พี่ๆ ให้ความสำคัญกับจุดไหนที่สุดครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "คนที่ใช้งาน iPhone 15 ราคา 26,900 บาทอยู่ รู้สึกว่าพอร์ต USB-C กับกล้อง 48MP ช่วยให้ถ่ายโอนและจัดการไฟล์ภาพได้สะดวกกว่ารุ่นเดิมชัดเจนไหมครับ? สำหรับสมาร์ทโฟนราคาสูงแบบนี้ ผมมองว่าการเลือกซื้อเครื่องศูนย์ไทยแท้ที่มีประกันศูนย์ 1 ปีเต็มจากร้านค้าทางการ Shopee Mall มั่นใจได้ 100% เรื่องของแท้และบริการหลังการขาย ไม่ต้องเสี่ยงกับเครื่องย้อมแมวครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": true}</t>
+          <t>{"last_personas": ["H", "B", "A", "D", "E", "H", "G", "D", "G", "A", "D", "D", "A", "H", "H", "B", "C", "H", "G", "A", "G", "E", "E", "H", "G", "G", "H", "B", "E", "H", "E", "G", "E", "E", "D", "E", "B", "D", "G", "A", "E", "E", "D", "G", "A", "E", "B", "F", "G", "H"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เมื่อวานเพิ่งเจอ...", "เห็นคนพูดถึงเยอะเลยลอง", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "มีใครเป็นเหมือนผมไหม", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "โดนป้ายยามาอีกที", "ตอนแรกไม่ได้จะซื้อ", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ", "เปิดด้วยสถานการณ์ที่สินค้านี้น่าจะเหมาะ", "เปิดด้วยราคาเทียบกับฟังก์ชันที่ได้", "เปิดด้วยปัญหาเฉพาะที่สินค้าประเภทนี้แก้", "เปิดด้วยจุดเด่นจริงหนึ่งข้อจากข้อมูล", "เปิดด้วยคำถามเฉพาะถึงคนที่เคยใช้จริง", "เปิดด้วยข้อที่ควรตรวจสอบก่อนซื้อ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "คำถาม", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "มุกเบาๆ", "เทียบข้อมูล", "มุกเบาๆ", "ปัญหาและทางเลือก", "มุกเบาๆ", "บอกต่อแบบกลางๆ", "คำถามเฉพาะ", "มุกเบาๆ", "คำถามเฉพาะ", "เทียบข้อมูล", "ปัญหาและทางเลือก", "บอกต่อแบบกลางๆ", "เทียบข้อมูล", "เทียบข้อมูล", "บอกต่อแบบกลางๆ"], "last_roles": ["R5", "R2", "R4", "R6", "R3", "R2", "R2", "R5", "R8", "R8", "R5", "R6", "R5", "R4", "R5", "R7", "R1", "R6", "R4", "R3", "R5", "R1", "R7", "R2", "R5", "R5", "R3", "R7", "R3", "R1", "R6", "R2", "R3", "R6", "R2", "R3", "R4", "R4", "R5", "R7", "R5", "R7", "R8", "R7", "R6", "R3", "R6", "R7", "R1", "R4"], "recent_captions": ["มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KLAY Cigar แท่งเซรามิกกระจายกลิ่น Ceramic ราคาแค่ 1088 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ แก้วเก็บความเย็น แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 339 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โซฟาเบดผ้าลูกฟูก รุ่น sunya สามารถปรับนอนได้ ราคาแค่ 6999 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชุดหม้อสแตนเลส ใบ พร้อมฝาปิด ชุดหม้อทำครัว ราคาแค่ 143 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปั๊มลม PUMA 2สูบ - ราคาแค่ 21550 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SA เครื่องฉีดน้ำแรงดันสูง เครื่องฉีดนํ้า เครื ราคาแค่ 1355 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ เก้าอี้สุขภาพ ดีๆครับ ตัวนี้มีจุดเด่นคือ Mobi GARDEN เก้าอี้ปิกนิก พับได้ ราคาแค่ 926 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง รับประกัน ปีเลื่อยไฟฟ้าไร้สาย นิ้ว เลื่อยโซ่ไ ราคาแค่ 964 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง เก้าอี้สุขภาพ ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก้าอี้พักผ่อน Minimal โซฟา ปรับนอนได้ ราคาแค่ 1499 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 545 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ลดสูงสุด % BsaB โฉมเก่า ราคาแค่ 895 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น FDM พร้อมส่ง พับได้ มุ้งกันยุง ราคาแค่ 156 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ชั้นวางของแบบตัวดูดสูญญากาศ แบบเข้ามุมติดผนัง ราคาแค่ 169 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ เครื่องนอน ดีๆครับ ตัวนี้มีจุดเด่นคือ เตียงพับได้ เตียงเสริม เตียงนอนสามารถพับได้ ส ราคาแค่ 810 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ตะกร้าใส่ของอเนกประสงค์ Keyway รุ่น - ราคาแค่ 49 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง เครื่องนอน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เตียงเป่าลม อัตโนมัติ ที่นอนลมกลางแจ้ง พับได้ ราคาแค่ 829 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿829", "เห็นคนพูดถึงเยอะเลยลอง มีใครกำลังเจอปัญหากระดาษเช็ดหน้าสากๆ จนแสบผิวเหมือนกันบ้างไหมครับ? พอดีผมบังเอิญไปเจอ ทิชชู่เช็ดหน้า สัมผัสนุ่ม คุณภาพสูง ตัวนี้กำลังจัดโปรลดราคาเหลือแค่ 109 บาท ได้ตั้ง 5 แพ็ค เลยลองกดมาใช้แล้วชอบความอ่อนโยนต่อผิวมาก ใครที่กำลังตามหา ทิชชู่หนานุ่ม สำหรับผิวแพ้ง่าย อยู่ เซฟเก็บไว้ดูตอนช้อป กันได้เลยนะครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿109", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ลวดหนาม ชุบกัลวาไนซ์ ยาว120- เบอร์ ราคาแค่ 710 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿710", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกผมก็ลังเลอยู่นานกับ เก้าอี้พักผ่อน ราคา 1499 บาทตัวนี้ เพราะกลัวว่าเบาะจะบางจนนั่งแล้วเจ็บก้น แต่พอตัดสินใจสอย รุ่น Minimal สีครีม มาลอง ปรากฏว่า เบาะหนา 10 ซม. ของเขาหนานุ่มใช้ได้เลย แถมยังเป็น เก้าอี้ปรับนอน ได้ถึง 160 องศา เอนหลังสบายจนผมเกือบหลับไปหลายรอบแล้ว ใครที่หาเก้าอี้นั่งเล่นอยู่ เซฟเก็บไว้ดูตอนช้อป หรือแชร์ไปชวนเพื่อนมานั่งด้วยกันได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1499", "ลองแล้วเข้าใจเลยว่าทำไมขายดี เมื่อก่อนร้านผมเงียบมาก ลูกค้าเดินผ่านไปมาโดยไม่รู้ว่าร้านเข้าร่วมโครงการของรัฐ ทำให้ยอดขายไม่ขยับเลยครับ ตอนนี้คนสังเกตเห็นร้านง่ายขึ้นเยอะ แวะเข้ามาสแกนจ่ายเงินกันสะดวกกว่าเดิมเพราะผมใช้ ป้ายฟิวเจอร์บอร์ด ที่เป็น ป้ายร้านร่วมโครงการรัฐ รุ่น คนละครึ่งพลัส ตัวนี้ที่มีขนาดให้เลือกทั้ง A4 และ A3 ในราคาแค่ 69 บาท พ่อค้าแม่ค้าคนไหนที่เจอปัญหานี้อยู่ลองแชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿69", "มีใครเป็นเหมือนผมไหม \n\nตอนแรกผมไม่ค่อยแน่ใจในคุณภาพของน้ำยาขจัดคราบ MARS ตัวนี้เลย แต่เพราะคราบกระจกห้องน้ำที่บ้านมันมัวจนผมส่องไม่เห็นความหล่อตัวเองแล้ว เลยยอมควักเงิน 249 บาทมาลองพิสูจน์ดูครับ ปรากฏว่าพวกคราบหินปูนและคราบน้ำบนกระจกที่เคยขัดจนกล้ามขึ้นก็ยังไม่ออก กลับเช็ดออกง่ายเฉยเลย ไม่ต้องถูจนเอวเคล็ดอีกต่อไปครับ ใครที่กำลังหาวิธีกำจัดคราบน้ำกระจกอยู่ เซฟโพสต์นี้เก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿249", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง เครื่องตัดหญ้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พับได้ ไร้สาย แบต 2 ก้อน ราคาแค่ 729 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿729", "ไม่คิดว่าจะตื่นมาพร้อมสภาพคอเคล็ดเหมือนโดนถีบตกเตียงทุกเช้า แถมเสียงกรนของผมก็ดังจนคนข้างๆ ระแวงว่าเปิดโรงงานโม่หินไว้ใต้เตียงครับ จนกระทั่งได้ลองเปลี่ยนมานอน หมอนสุขภาพ รุ่น Deep Sleep ราคา 1690 บาท ตัวนี้ที่เข้ามาช่วยลดปวดคอ แล้วก็ช่วยลดการกรน ได้ตรงจุดพอดี ใครที่กำลังเจอปัญหาปวดบ่าปวดคอตอนตื่นนอนหรือโดนคนข้างๆ บ่นเรื่องเสียงกรน ลองเซฟโพสต์นี้ไว้ดูหรือแชร์ต่อให้เพื่อนสายกรนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1690", "โดนป้ายยามาอีกที มีใครในบ้านที่ชอบดื่มน้ำเย็นทั้งวันแล้วเจอปัญหาน้ำแข็งละลายไวบ้างไหมครับ? ผมเลยจัดแก้วเก็บความเย็น TYESO 2026 ขนาด 900ML มาให้คนที่บ้านได้ใช้ ตัวนี้เก็บเย็น 24H และเก็บร้อน 12H ในราคา 319 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้คนในครอบครัวได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿319", "ตอนแรกไม่ได้จะซื้อ เพราะผมเคยคิดว่ากระดาษทิชชู่ทั่วไปเปียกน้ำนิดหน่อยก็เปื่อยขาดติดมือตลอด แต่พอเปิดใจลองเอามาเช็ดคราบน้ำเปียกๆ ดู ปรากฏว่าเนื้อกระดาษเหนียว ไม่ขาดคามือเลยครับ มันคือกระดาษทิชชู่หนาพิเศษ ทนน้ำ ที่ช่วยแก้ปัญหานี้ได้จริงๆ ได้มา 10 แพ็ค ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้กันครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "เมื่อวานเพิ่งเจอหญ้าหลังบ้านยาวรกเต็มไปหมด แถมการต้องมาทนเหนื่อยตัดหญ้าแบบเดิมๆ มันทั้งเมื่อยล้าและเสียเวลาชีวิตสุดๆ ตอนแรกผมก็นั่งลังเลอยู่นานเพราะไม่แน่ใจว่าพวกเครื่องตัดหญ้าไร้สายมันจะใช้งานได้จริงไหม หรือซื้อมาแล้วจะตัดไม่เข้า สรุปเลยลองสั่ง Makita 388Vf ราคา 1,575 บาท ที่มีระบบดูอัลแอคชั่นมาใช้ดู ปรากฏว่าช่วยเบาแรงไปได้เยอะมาก ใครกำลังเจอปัญหานี้อยู่ลองเซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1575", "เห็นคนพูดถึงเยอะเลยลองจัดเครื่องฉีดน้ำแรงดันสูง รุ่น AMAZON ULTRA มาไว้ให้คนที่บ้านใช้ครับ ตัวนี้มาพร้อมแรงดัน 80-120 บาร์ แถมมีรับประกัน 1 ปี กะว่าจะซื้อมาทุ่นแรง แต่สรุปผมโดนยึดไปใช้ฉีดล้างพื้นล้างรถอยู่คนเดียวซะงั้น ค่าตัวอยู่ที่ 4620 บาท พ่อบ้านคนไหนที่มองหาเครื่องฉีดน้ำแรงดันสูงล้างรถติดบ้านไว้ ลองเซฟโพสต์นี้เก็บไว้ดูตอนช้อปได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿4620", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังมองหาแก้วเซรามิกไว้ใช้ใส่น้ำหรือวางตกแต่งคาเฟ่ที่บ้านอยู่ไหมครับ? ผมกดสั่งออนไลน์รุ่น Miffy ลายการ์ตูน Miffy ใบนี้มาราคา 337 บาท พอได้ลองใช้งานจริงมาระยะหนึ่งแล้วประทับใจเลย เซฟเก็บไว้ดูตอนช้อปหรือกดแชร์ต่อให้เพื่อนที่ชอบสะสมแก้วได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿337", "กำลังหาของแบบนี้อยู่พอดี เมื่อก่อนเวลาผมทำน้ำหกบนโต๊ะทีไร ใช้ทิชชู่ธรรมดาเช็ดแล้วชอบเปื่อยขาดติดมือจนเลอะเทอะไปหมดครับ แต่พอเปลี่ยนมาใช้กระดาษทิชชู่แขวนอันนี้ ชีวิตสะดวกขึ้นเยอะเลยครับ เพราะเนื้อกระดาษหนาพิเศษ ทนน้ำ เช็ดรอยเปียกได้หมดจดโดยไม่เปื่อยคามือ ได้มาแบบ 5 แพ็ค ในราคา 89 บาท ช่วยแก้ปัญหาเช็ดน้ำเลอะในชีวิตประจำวันได้ตรงจุดมากๆ แชร์ต่อให้เพื่อนที่เจอปัญหานี้หรือเซฟเก็บไว้ดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿89", "ลองแล้วเข้าใจเลยว่าทำไมขายดี บ้านไหนกำลังมองหาเครื่องตัดหญ้าเบนซินเอาไว้ให้คนที่บ้านใช้ดูแลสวนกันบ้างครับ? พอดีผมไปเจอเครื่องตัดหญ้า 4 จังหวะ รุ่น GX-35 ตัวนี้มา เป็นเครื่องขนาดเล็ก ราคา 2,560 บาท ลองเซฟโพสต์นี้หรือแชร์ไปให้คนในบ้านช่วยกันดูได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿2560", "มีใครเป็นเหมือนผมไหม ที่วันหยุดทีไรต้องมานั่งออกแรงขัดพื้นกับล้างรถจนปวดหลังไปหมด จนผมเปลี่ยนมาใช้ เครื่องฉีดน้ำแรงดันสูง ZINSANO AD ขนาด 110-180 บาร์ ตัวนี้ที่มีมอเตอร์ Induction ทนทาน มาช่วยฉีดคราบออกอย่างไว ราคาอยู่ที่ 9790 บาท ใครที่กำลังเจอปัญหานี้เหมือนกัน ลองเซฟโพสต์นี้เก็บไว้หรือแชร์ต่อให้เพื่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿9790", "อันนี้เกินคาดจริงๆ ตอนแรกผมลังเลอยู่นานเพราะกลัวว่าสั่งออนไลน์แล้วจะได้น้องหน้าเบี้ยว แต่พอลองสั่งตุ๊กตาราคา 889 บาทตัวนี้มา งานเรียบร้อยน่ารักจนผมแอบรู้สึกผิดที่เคยไประแวงเขาครับ แถมทางร้านเขามีแบบพร้อมส่ง และยังช่วยเขียนการ์ดฟรีให้อีก ใครกำลังหาของขวัญน่ารักๆ ลองแชร์โพสต์นี้เก็บไว้ดูตอนเลือกซื้อกันได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿889", "ไม่คิดว่าจะเจอปัญหาเหมือนผมไหมครับ เวลาต้องเตรียมเครื่องดื่มไว้ดื่มทั้งวันแล้วชอบชืดหรือละลายไวเกินไป? พอได้มาเจอ ถังเก็บความเย็น และ ถังเก็บความร้อน ที่ทำจาก สแตนเลส ขนาด 6-12 ลิตร ตัวนี้ก็ช่วยแก้ปัญหาเรื่องอุณหภูมิเครื่องดื่มไปได้เยอะเลย ในราคา 389 บาท ใครเจอปัญหาแบบนี้อยู่ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿389", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง เครื่องมือช่าง/ทำสวน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องตัดหญ้าสะพายบ่า NIPPON | ./ ราคาแค่ 1896 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿1896", "ตอนแรกไม่ได้จะซื้อ แก้วเก็บความเย็นตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ TYESO -/MTumbler พร้อมที่จับ,ขวดน้ําฉนวนสุญญา ราคาแค่ 349 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿349", "ปัญหากระเป๋าเดินทางซิปแทบแตกน่าจะเบาลงได้ถ้าเน้นประหยัดพื้นที่ ซึ่งผมกำลังดูข้อมูลถุงสูญญากาศแบบใสที่พกพาสะดวกในราคาใบละ 10 บาทอยู่ครับ สำหรับทุกคนแล้ว ถุงสูญญากาศแบบใสราคา 10 บาทนี้ ตอบโจทย์เรื่องการประหยัดพื้นที่ตอนพกพาไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "บ้านไหนที่กำลังหาของใช้สำหรับโซนห้องน้ำ ชั้นวางของราคา 65 บาทตัวนี้ระบุจุดเด่นว่าระบายน้ำได้และวางในที่เปียกได้ครับ คนที่เคยใช้งานจริง ตัวฟังก์ชันระบายน้ำในที่เปียกทำงานได้ตรงตามข้อมูลไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจซื้อตู้เพิ่มเพราะเสื้อผ้าเริ่มล้นจนแทบแย่งที่นอน ลองเช็กพื้นที่จัดเก็บดูก่อนว่าถุงสูญญากาศแบบมีวาล์วที่ช่วยประหยัดพื้นที่และใช้ซ้ำได้ใบละ 17 บาทนี้เหมาะกับตู้ที่บ้านไหมครับ ถ้าเป็นพี่จะเอาถุงสูญญากาศมีวาล์วราคา 17 บาทนี้ไปจัดการกับผ้านวมผืนใหญ่หรือกองเสื้อผ้าก่อนครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่เจอปัญหาเสื้อผ้าแขวนทิ้งไว้นานจนฝุ่นเกาะ ถุงคลุมเสื้อผ้าแบบหนาพิเศษ 2 ชั้น กันฝุ่นกันยับมีซิป และมีให้เลือก 4 ขนาด ในราคา 21 บาทนี้น่าจะเป็นอีกตัวเลือกครับ ผมอยากถามคนที่เคยใช้ว่าความหนา 2 ชั้นกับตัวซิปของรุ่นนี้กันฝุ่นและรูดใช้งานได้ดีตามสเปกไหมครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่ายแค่ 11 บาทแต่ได้ถุงสูญญากาศแบบซิปล็อค 2 ชั้นที่เนื้อหนาพิเศษและใช้ซ้ำได้ ช่วยแก้ปัญหาคนจัดกระเป๋าเดินทางที่ต้องขึ้นไปนั่งทับเพื่อรูดซิปปิดครับ พี่คิดว่าถุงราคา 11 บาทที่ให้ซิป 2 ชั้นแบบนี้จะช่วยประหยัดพื้นที่เสื้อผ้าได้เยอะไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครเจอปัญหาเสื้อผ้าล้นกระเป๋าจนจัดไม่ลง ผมมองว่าถุงสูญญากาศ ลายแบร์บริค ที่มีซิปล็อค2ชั้นมีวาล์ว ช่วยประหยัดพื้นที่ ในราคา 11 บาท น่าจะเหมาะกับคนที่กำลังหาตัวช่วยแพ็กของเดินทางครับ\n\nราคา 11 บาทกับซิปล็อค2ชั้นมีวาล์วแบบนี้ ตอบโจทย์การจัดกระเป๋าของพี่ๆ ไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "การออกแบบที่มีวาล์วช่วยให้บีบอัดและประหยัดพื้นที่จัดเก็บได้ง่ายขึ้น โดยถุงสูญญากาศชิ้นนี้ราคาอยู่ที่ 9 บาทครับ ด้วยฟังก์ชันมีวาล์วในราคา 9 บาท คิดว่าจะเอาไปใช้ประหยัดพื้นที่เสื้อผ้าในตู้หรือในกระเป๋าเดินทางมากกว่ากันครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหามือถือค้างตอนกำลังจะกดจ่ายเงินแล้วอยากเปลี่ยนมาใช้ iPhone 18 Pro Max ราคา 48,900 บาท สิ่งที่ผมอยากให้ตรวจเช็กให้ดีก่อนตัดสินใจคือต้องเลือกร้านค้าทางการ Shopee Mall เพื่อให้ได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม จะได้อุ่นใจเรื่องบริการหลังการขายและไม่เสี่ยงเจอเครื่องย้อมแมวครับ\n\nคนที่ได้สัมผัสชิป A20 Pro เครื่องจริงไปแล้ว มองว่าความเร็วในการประมวลผลต่างจากรุ่นก่อนเยอะไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จุดที่ผมอยากให้เช็กก่อนคือความแข็งแรงของตัวล็อก ตัวนี้เป็นที่วางแก้วหนีบโต๊ะ ราคา 97 บาท ที่ระบุจุดเด่นว่าหมุนได้ 360 องศาและปรับได้ 3 ระดับครับ\n\nคนที่ใช้อยู่จริง พอปรับระดับแล้วหมุน 360 องศาไปมา ตัวหนีบยังยึดกับโต๊ะได้แน่น ไม่เลื่อนหลุดใช่ไหมครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สำหรับคนที่กำลังมองหาสมาร์ตโฟนสเปกแรง การเลือกรุ่นราคาสูงอย่าง iPhone 17 Pro ราคา 39,900 บาท ผ่านร้านค้าทางการ Shopee Mall ทำให้ไว้ใจได้ 100% ว่าได้เครื่องศูนย์ไทยแท้พร้อมประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องหิ้วหรือโดนโกงเรื่องบริการหลังการขายครับ ผมอยากถามคนที่เคยใช้งานจริงว่าชิป A19 Pro ควบคู่กับจอ ProMotion 120Hz เวลาเปิดกราฟิกสูงต่อเนื่อง มีอาการหน่วงหรือแบตเตอรี่ลดไวกว่าปกติไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "จ่าย 14 บาทแล้วได้ขวดเครื่องปรุงที่มีช้อนตักในตัว ผมว่าก็น่าสนใจสำหรับคนที่เจอปัญหาช้อนจมหายหรือเลอะเทอะเวลาหยิบใช้ครับ คิดว่าขวดเครื่องปรุงราคา 14 บาทที่มีฟังก์ชันช้อนในตัวแบบนี้จะตักใช้งานได้สะดวกจริงไหมครับ? ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ใครที่เจอปัญหาแบตมือถือหมดไวระหว่างวัน การเลือกซื้อสมาร์ตโฟนราคาสูงอย่าง iPhone 16 Plus จุดเด่นจอใหญ่ แบตอึด ชิป A18 ในราคา 34,900 บาท ผ่านร้านค้าทางการ Apple Flagship Store บน Shopee Mall ทำให้ไว้ใจได้ 100% ว่าเป็นเครื่องศูนย์ไทยแท้ มีประกันศูนย์ 1 ปีเต็ม ไม่ต้องเสี่ยงกับเครื่องย้อมแมวและอุ่นใจเรื่องบริการหลังการขายครับ \n\nคนที่ใช้งานจริงอยู่ อยากทราบว่าชิป A18 ตัวนี้ช่วยจัดการพลังงานให้แบตเตอรี่ใช้งานทั่วไปพ้นวันโดยไม่ต้องพกที่ชาร์จสำรองได้จริงไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "สรุปข้อมูลของ แฟ้มเอกสาร ตัวนี้แบบสั้นๆ คือ 12 หน้า กันฝุ่นและความชื้น ราคา 69 บาทครับ ถ้าต้องเลือก แฟ้มเอกสาร สักตัว พี่ๆ ให้ความสำคัญกับจุดไหนที่สุดครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "คนที่ใช้งาน iPhone 15 ราคา 26,900 บาทอยู่ รู้สึกว่าพอร์ต USB-C กับกล้อง 48MP ช่วยให้ถ่ายโอนและจัดการไฟล์ภาพได้สะดวกกว่ารุ่นเดิมชัดเจนไหมครับ? สำหรับสมาร์ทโฟนราคาสูงแบบนี้ ผมมองว่าการเลือกซื้อเครื่องศูนย์ไทยแท้ที่มีประกันศูนย์ 1 ปีเต็มจากร้านค้าทางการ Shopee Mall มั่นใจได้ 100% เรื่องของแท้และบริการหลังการขาย ไม่ต้องเสี่ยงกับเครื่องย้อมแมวครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ก่อนตัดสินใจลองเช็กพื้นที่ผนังข้างโต๊ะกันก่อนนะครับ ผมมองว่าแผ่นรูจัดระเบียบตัวนี้น่าจะเหมาะกับคนที่อยากจัดระเบียบโต๊ะ โดยมีพร้อมชุดติดตั้งมาให้ในราคา 43 บาท\n\nในงบ 43 บาทที่ได้พร้อมชุดติดตั้ง คิดว่าแผ่นรูจัดระเบียบนี้จะเพียงพอกับอุปกรณ์บนโต๊ะของคุณไหมครับ?\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"], "last_posted_is_iphone": false}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -5287,6 +5287,11 @@
           <t>฿26.00</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>done 2026-09-27T02:46:04.532285+00:00 live-graphics 116701184708556_1028671816859861</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
